--- a/plantilla_datos_centro.xlsx
+++ b/plantilla_datos_centro.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lydia.alvarez\Desktop\TFG\Nube\Simulacion 5. Distancia media ssegun centro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lydia.alvarez\Desktop\TFG\Nube\Simulacion 6. ahora lee hoja escenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7462CF-612F-4247-B39F-F9987FF5033A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC60ED2D-8BAE-4A17-8657-9E566B7B815A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Leer" sheetId="1" r:id="rId1"/>
@@ -49,172 +49,6 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Identificador del centro. Solo para tus informes, no afecta al cálculo.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Nº de plazas ocupadas del centro. Debe coincidir con la suma de residentes de la hoja Zonas_Layout.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Si tienes registro interno de incidencias de al menos 1 año, úsalo: (nº caídas registradas) / (nº residentes). Si no lo tienes, usa el valor de referencia de la literatura española.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tiempo cronometrado recorriendo un pasillo de longitud conocida a paso rápido (sin correr), o usa el valor por defecto (~4,2 km/h, marcha rápida profesional).</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Margen aleatorio sobre el tiempo de desplazamiento calculado, para representar obstáculos, tráfico de pasillo, ascensores ocupados, etc. 0,20 = variación de ±20%.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Cronometraje del protocolo de valoración tras llegar junto al residente (constantes, valoración, decisión). Mínimo observado.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Igual que el anterior, pero el máximo observado (casos más complejos).</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>(nº de traslados por caída) / (nº de caídas totales) de tu registro interno, si lo tienes. Si no, usa el valor por defecto, coherente con los rangos de tu ficha técnica.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000009000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Hipótesis de mejora clínica: menos tiempo en el suelo implica menos complicaciones graves. No es una medición — es una reducción relativa razonada, ajústala con prudencia.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Normalmente 365 (un año). Súbelo solo si quieres simular varios años seguidos.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Más réplicas = intervalos de confianza más estrechos, pero más tiempo de cálculo. 300 es un buen equilibrio para un TFG.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Fija el punto de partida del generador aleatorio para que el resultado sea reproducible. Cámbiala solo si quieres comprobar la estabilidad del resultado con otra secuencia.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000D000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Fracción del personal libre que, en un instante dado, está en realidad ocupada en una tarea asistencial NO interrumpible con otro residente (aseo, alimentación, movilización con grúa, medicación) y no puede acudir de inmediato -- debe ir otro compañero disponible. SUPUESTO razonado (no medido): estimar con un estudio de muestreo de trabajo (observaciones puntuales aleatorias a lo largo de turnos, contabilizando en qué tarea está cada trabajador en ese instante) para sustituir por un dato real.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
     <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
@@ -231,143 +65,33 @@
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Unknown Author</author>
+    <author>LYDIA ALVAREZ ALCALDE</author>
   </authors>
   <commentList>
-    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{54D17A0A-199F-4C30-91EB-F2F833C9FB7D}">
       <text>
         <r>
           <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Valores posibles:
-· 'ronda_manual_o_boton' — el personal detecta la caída en rondas periódicas, o si el residente puede pulsar un botón FIJO en la pared/habitación (no lo lleva encima).
-· 'sensor_ambiental_auto' — un sensor instalado en el entorno (p. ej. radar de techo) detecta la caída automáticamente, sin ninguna acción del residente. Es el caso de un radar mmWave de techo.
-· 'dispositivo_manual' — el residente lleva un dispositivo encima (pulsera SOS, colgante) y debe pulsarlo él mismo para generar la alerta; si no puede (inconsciente, deterioro cognitivo, no lo lleva puesto), no hay detección automática y se recurre a la ronda manual.</t>
+          <t>LYDIA ALVAREZ ALCALDE:</t>
         </r>
-      </text>
-    </comment>
-    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
-      <text>
         <r>
           <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Fracción de caídas en las que nadie ve al residente caer en el momento (habitualmente porque ocurre en la habitación, en soledad). Solo se usa si el modo es 'ronda_manual_o_boton'.
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Cada cuántos minutos se pasa por cada habitación en turno de día si no hay alerta automática. Solo aplica al escenario que use 'ronda_manual_o_boton'.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Igual que el anterior, en turno de noche (normalmente más largo, con menos personal).</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tiempo mínimo estimado desde que se pulsa el botón hasta que el aviso llega a algún dispositivo del personal.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Tiempo máximo estimado para el mismo proceso.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Latencia de procesamiento y aviso del sistema (no la detección física del sensor, que suele ser &lt;1 s, sino el tiempo hasta que la alerta llega al terminal del personal).</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Igual que el anterior, tiempo máximo. Revisa la ficha técnica de tu proveedor de sensores.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Solo aplica si el modo To-Be es 'dispositivo_manual'. Probabilidad de que, en el momento de caer, el residente esté consciente, lleve el dispositivo puesto y pueda pulsarlo. Depende del grado de dependencia/deterioro cognitivo de tu población. Si no aplica, déjalo en blanco.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Nº medio de incidencias que se fuerzan dentro de la ventana de 4h para el escenario de estrés. El script genera este número de incidencias distribuidas aleatoriamente dentro de la ventana en cada réplica (proceso de Poisson calibrado a esta media).</t>
+          <t xml:space="preserve">
+Nº medio de incidencias que se fuerzan dentro de la ventana de 4h para el escenario de estrés. El script genera este número de incidencias distribuidas aleatoriamente dentro de la ventana en cada réplica (proceso de Poisson calibrado a esta media). Se fuerzan 8 por defecto.</t>
         </r>
       </text>
     </comment>
@@ -376,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="164">
   <si>
     <t>Qué es este archivo</t>
   </si>
@@ -387,15 +111,6 @@
     <t>1. Haz una copia de este archivo con el nombre de tu centro.</t>
   </si>
   <si>
-    <t>2. Sustituye los valores en texto AZUL por los datos reales de tu centro. El texto negro son cabeceras/fórmulas, no los toques.</t>
-  </si>
-  <si>
-    <t>3. Cada celda editable tiene un comentario (triángulo rojo en la esquina) explicando qué dato es y cómo recogerlo si no lo tienes a mano.</t>
-  </si>
-  <si>
-    <t>5. Guarda el archivo y pásale la ruta al script Python (ver README_como_ejecutar.md).</t>
-  </si>
-  <si>
     <t>Estructura del archivo</t>
   </si>
   <si>
@@ -420,9 +135,6 @@
     <t>OnaCare</t>
   </si>
   <si>
-    <t>texto</t>
-  </si>
-  <si>
     <t>Identificador del centro. Solo para tus informes, no afecta al cálculo.</t>
   </si>
   <si>
@@ -456,9 +168,6 @@
     <t>m/min</t>
   </si>
   <si>
-    <t>Tiempo cronometrado recorriendo un pasillo de longitud conocida a paso rápido (sin correr).</t>
-  </si>
-  <si>
     <t>Cálcul orealizado según muestras recogidas de simulaciones realizadas en el centro.</t>
   </si>
   <si>
@@ -481,9 +190,6 @@
   </si>
   <si>
     <t>Cronometraje del protocolo de valoración tras llegar junto al residente (constantes, valoración, decisión). Mínimo observado.</t>
-  </si>
-  <si>
-    <t>SUPUESTO razonado, cruzado con dos fuentes propias del TFG: (1) apdo. 4.2, estimación de campo de 18-25 min/incidencia para el proceso completo aviso+desplazamiento+valoracion+parte+llamada medico, del cual se resta el resto de componentes ya cuantificados en KPI-2/KPI-3 para aislar la valoracion in situ; (2) encuesta sectorial Q34/Q61 (tiempo detección emergencia -&gt; salida del paciente del centro), donde la moda de las respuestas reales es "entre 10 y 30 minutos", orden de magnitud consistente.</t>
   </si>
   <si>
     <t>Tiempo de atención in situ (máximo)</t>
@@ -538,12 +244,6 @@
     <t>Probabilidad de ocupación en tarea no interrumpible</t>
   </si>
   <si>
-    <t>Fracción del personal libre que, en un instante dado, está en realidad ocupada en una tarea asistencial NO interrumpible con otro residente (aseo, alimentación, movilización con grúa, medicación) y no puede acudir de inmediato -- debe ir otro compañero disponible. SUPUESTO razonado (no medido): estimar con un estudio de muestreo de trabajo (observaciones puntuales aleatorias a lo largo de turnos, contabilizando en qué tarea está cada trabajador en ese instante) para sustituir por un dato real.</t>
-  </si>
-  <si>
-    <t>Define los módulos/plantas/alas del centro. El modelo usa esto para calcular cuánto tarda el personal en llegar a una caída SEGÚN dónde ocurre y dónde está el personal en ese momento.</t>
-  </si>
-  <si>
     <t>Zona</t>
   </si>
   <si>
@@ -592,18 +292,6 @@
     <t>Comentarios sobre esta hoja:</t>
   </si>
   <si>
-    <t>· 'Distancia a control' = distancia media caminando desde el puesto de control/enfermería hasta el centro de esa zona (medida sobre plano, con podómetro, o estimada a pasos).</t>
-  </si>
-  <si>
-    <t>· 'Personal turno DÍA/NOCHE es el nº de auxiliares/enfermeras cuya base está en esa zona durante ese turno cuando no están atendiendo ninguna incidencia. La suma debe coincidir con el personal total de día/noche que definas para la simulación.</t>
-  </si>
-  <si>
-    <t>· Puedes añadir o quitar filas de zonas; el script lee todas las filas entre la cabecera y la fila TOTAL, así que inserta filas nuevas por encima de la fila TOTAL.</t>
-  </si>
-  <si>
-    <t>· 'Distancia intra-zona' = distancia media que recorre el personal DENTRO de la misma zona donde ya se encuentra (p. ej., de una habitación a otra del mismo módulo), a diferencia de 'Distancia a control', que es hasta el punto de control/enfermería.</t>
-  </si>
-  <si>
     <t>As-Is</t>
   </si>
   <si>
@@ -649,12 +337,6 @@
     <t>Igual que el anterior, tiempo máximo. Revisa la ficha técnica de tu proveedor de sensores.</t>
   </si>
   <si>
-    <t>Prob. de poder activar dispositivo manual</t>
-  </si>
-  <si>
-    <t>Solo aplica si el modo To-Be es 'dispositivo_manual'. Probabilidad de que, en el momento de caer, el residente esté consciente, lleve el dispositivo puesto y pueda pulsarlo. Depende del grado de dependencia/deterioro cognitivo de tu población. Si no aplica, déjalo en blanco.</t>
-  </si>
-  <si>
     <t>De las caidas NO presenciadas en el momento, fraccion que aun asi se detecta pronto porque alguien oye un golpe o un grito de ayuda (sin haber visto la caida). Turno DIA.</t>
   </si>
   <si>
@@ -676,9 +358,6 @@
     <t>Fraccion de caidas que el radar mmWave NO detecta (falso negativo). Al fallar, la deteccion recae en el mismo mecanismo humano que en As-Is (oido o ronda), ya que el entorno acustico del edificio no cambia por instalar el sensor.</t>
   </si>
   <si>
-    <t>Literatura ya citada en el apdo. 5 de la memoria: precision del radar mmWave IWR6843 &gt;95% (Sun et al., 2020) -&gt; se asume el 5% restante como falso negativo.</t>
-  </si>
-  <si>
     <t>Los 3 escenarios operativos que se simulan por separado, además del análisis anual completo.</t>
   </si>
   <si>
@@ -694,10 +373,6 @@
     <t>Duración del escenario</t>
   </si>
   <si>
-    <t>Nº incidencias objetivo
-(solo Escenario 3)</t>
-  </si>
-  <si>
     <t>Personal disponible</t>
   </si>
   <si>
@@ -722,9 +397,6 @@
     <t>Personal turno NOCHE (hoja Zonas_Layout)</t>
   </si>
   <si>
-    <t>Brote gastrointestinal o episodio de agitación grupal: varias incidencias concentradas en pocas horas, con el personal de noche ya reducido.</t>
-  </si>
-  <si>
     <t>Ventana de 4 horas (simulación independiente, no forma parte de la tasa media anual)</t>
   </si>
   <si>
@@ -779,15 +451,6 @@
     <t>Ningún sensor tiene una precisión del 100%: una fracción de las caídas es un falso negativo del sensor (p_fallo_sensor). En ese caso residual, la detección recae en el mismo mecanismo humano que en As-Is (oír al residente, o la ronda), ya que el entorno acústico del edificio no cambia por instalar el sensor. Con una precisión &gt;95% (ver apdo. 5 de la memoria, radar mmWave IWR6843, Sun et al., 2020) esta vía apenas pesa en el resultado agregado, pero se mantiene por coherencia con el modelo As-Is y para no asumir una fiabilidad del 100% que ningún fabricante garantiza.</t>
   </si>
   <si>
-    <t>Dentro de las caídas "no presenciadas" (nadie la ve en el momento), una parte se detecta igualmente pronto porque alguien oye un golpe o un grito de ayuda sin haber visto la caída en sí. Esta probabilidad depende del turno: de noche hay más silencio ambiental y el auxiliar de planta está más cerca; de día hay más ruido de fondo (televisión, comidas, conversaciones) y el personal está más disperso en tareas simultáneas. [Supuesto razonado, ver hoja Deteccion]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPUESTO razonado (no medido): se estima mayor probabilidad de deteccion acustica incidental de noche (silencio ambiental, 1 auxiliar de planta mas cerca) que de dia (ruido de fondo: TV, comidas, conversaciones; personal disperso en tareas simultaneas). Coherente con el incidente observado en el apdo. 4.5.3 (caida no presenciada detectada al oir el grito de ayuda). </t>
-  </si>
-  <si>
-    <t>SUPUESTO razonado (no medido): se estima mayor probabilidad de deteccion acustica incidental de noche (silencio ambiental, 1 auxiliar de planta mas cerca) que de dia (ruido de fondo: TV, comidas, conversaciones; personal disperso en tareas simultaneas). Coherente con el incidente observado en el apdo. 4.5.3 (caida no presenciada detectada al oir el grito de ayuda).</t>
-  </si>
-  <si>
     <t>Cómo se detecta una caída en cada escenario. Esto determina cuánto tiempo pasa desde que ocurre la caída hasta que alguien se entera, antes de que el personal empiece a desplazarse.</t>
   </si>
   <si>
@@ -821,74 +484,152 @@
     <t>Intervalo de ronda - turno día (min)</t>
   </si>
   <si>
-    <t>Dato del centro (OnaCare) - política interna de frecuencia de rondas, editable por el centro.</t>
-  </si>
-  <si>
     <t>Probabilidad de traslado hospitalario - As-Is</t>
   </si>
   <si>
     <t>Probabilidad de traslado hospitalario - To-Be</t>
   </si>
   <si>
-    <t>SUPUESTO - ajustar con estudio de muestreo de trabajo</t>
-  </si>
-  <si>
     <t>Plantilla de datos - Simulación de eventos discretos (DES) de respuesta ante caídas</t>
   </si>
   <si>
-    <t>4. Las celdas con fondo amarillo son SUPUESTOS del modelo (no datos medidos) - revísalas con más atención, son las que más cambian el resultado si están mal calibradas.</t>
-  </si>
-  <si>
-    <t>· Parametros_Generales - datos globales del centro y de la simulación.</t>
-  </si>
-  <si>
-    <t>· Zonas_Layout - módulos/plantas del centro, nº de residentes y personal de cada uno, y las distancias que definen el layout físico.</t>
-  </si>
-  <si>
-    <t>· Deteccion - cómo se detecta una caída en cada escenario (ronda manual, botón, sensor automático, dispositivo llevado por el residente).</t>
-  </si>
-  <si>
-    <t>· Escenarios - define las ventanas horarias y condiciones de los 3 escenarios de tu TFG (día tipo, noche tipo, pico de incidencias).</t>
-  </si>
-  <si>
-    <t>· Hipotesis - lista en lenguaje llano de todos los supuestos que usa el modelo. Léela antes de confiar en los resultados.</t>
-  </si>
-  <si>
-    <t>· La columna To-Be debe reflejar el layout rediseñado (unidades de convivencia más pequeñas, sub-almacenes descentralizados, personal más repartido) - normalmente son distancias menores.</t>
+    <t>Escenario 1 - Día tipo</t>
+  </si>
+  <si>
+    <t>Escenario 2 - Noche tipo</t>
+  </si>
+  <si>
+    <t>Escenario 3 - Pico de incidencias nocturnas</t>
+  </si>
+  <si>
+    <t>Hipótesis del modelo - léelas antes de confiar en los resultados</t>
+  </si>
+  <si>
+    <t>La reducción de personal a caídas evitables por hospitalización (probabilidad de traslado) es una hipótesis clínica razonada (menos tiempo en el suelo → menos complicaciones), no una medición directa - trátala con prudencia en las conclusiones.</t>
+  </si>
+  <si>
+    <t>Detección sensor ambiental - máximo (seg)</t>
   </si>
   <si>
     <t>Valores posibles:
-· 'ronda_manual_o_boton' - el personal detecta la caída en rondas periódicas, o si el residente puede pulsar un botón FIJO en la pared/habitación (no lo lleva encima).
+· 'ronda_manual_o_boton' - el personal detecta la caída en rondas periódicas, o si el residente puede pulsar un botón fijo en la pared/habitación (no lo lleva encima).
 · 'sensor_ambiental_auto' - un sensor instalado en el entorno (p. ej. radar de techo) detecta la caída automáticamente, sin ninguna acción del residente. Es el caso de un radar mmWave de techo.
 · 'dispositivo_manual' - el residente lleva un dispositivo encima (pulsera SOS, colgante) y debe pulsarlo él mismo para generar la alerta; si no puede (inconsciente, deterioro cognitivo, no lo lleva puesto), no hay detección automática y se recurre a la ronda manual.</t>
   </si>
   <si>
-    <t>Escenario 1 - Día tipo</t>
-  </si>
-  <si>
-    <t>Escenario 2 - Noche tipo</t>
-  </si>
-  <si>
-    <t>Escenario 3 - Pico de incidencias nocturnas</t>
-  </si>
-  <si>
-    <t>Hipótesis del modelo - léelas antes de confiar en los resultados</t>
-  </si>
-  <si>
-    <t>La reducción de personal a caídas evitables por hospitalización (probabilidad de traslado) es una hipótesis clínica razonada (menos tiempo en el suelo → menos complicaciones), no una medición directa - trátala con prudencia en las conclusiones.</t>
-  </si>
-  <si>
-    <t>Este Excel reúne todos los datos de entrada que necesita el script 'simulacion_onacare_v5.py' para simular la respuesta ante caídas de cualquier centro geriátrico, no solo OnaCare. Viene pre-rellenado con los datos (reales y estimados, indicados en cada caso) de OnaCare, a modo de ejemplo funcional.</t>
-  </si>
-  <si>
-    <t>Detección sensor ambiental - máximo (seg)</t>
+    <t>2. Sustituye los valores en texto AZUL por los datos reales de tu centro. El texto negro son cabeceras/fórmulas, no los modifiques.</t>
+  </si>
+  <si>
+    <t>5. Guarda el archivo y pásale la ruta al script Python (ver ejecutar.md).</t>
+  </si>
+  <si>
+    <t>Deteccion: cómo se detecta una caída en cada escenario (ronda manual, botón, sensor automático, dispositivo llevado por el residente).</t>
+  </si>
+  <si>
+    <t>Zonas_Layout: módulos/plantas del centro, nº de residentes y personal de cada uno, y las distancias que definen el layout físico.</t>
+  </si>
+  <si>
+    <t>Parametros_Generales: datos globales del centro y de la simulación.</t>
+  </si>
+  <si>
+    <t>Hipotesis: lista en lenguaje llano de todos los supuestos que usa el modelo. Léela antes de confiar en los resultados.</t>
+  </si>
+  <si>
+    <t>Tiempo cronometrado recorriendo un pasillo de longitud conocida a paso rápido (sin correr).  Sino, usa el valor por defecto (~4,2 km/h, marcha rápida profesional).</t>
+  </si>
+  <si>
+    <t>3. Las celdas editables  se complementan con un comentario explicando qué dato es y cómo recogerlo si no lo tienes a mano.</t>
+  </si>
+  <si>
+    <t>Fracción del personal libre que, en un instante dado, está en realidad ocupado en una tarea asistencial no interrumpible con otro residente (aseo, alimentación, movilización con grúa, medicación) y no puede acudir de inmediato. Debe ir otro compañero disponible. SUPUESTO razonado (no medido): estimar con un estudio de muestreo de trabajo (observaciones puntuales aleatorias a lo largo de turnos, contabilizando en qué tarea está cada trabajador en ese instante) para sustituir por un dato real.</t>
+  </si>
+  <si>
+    <t>SUPUESTO razonado. Según la memoria del TFG: estimación de campo de 18-25 min/incidencia para el proceso completo aviso+desplazamiento+valoracion+parte+llamada medico, del cual se resta el resto de componentes ya cuantificados en KPI-2/KPI-3 para aislar la valoracion in situ; (2) encuesta sectorial Q34/Q61 (tiempo detección emergencia -&gt; salida del paciente del centro), donde la moda de las respuestas reales es "entre 10 y 30 minutos", orden de magnitud consistente.</t>
+  </si>
+  <si>
+    <t>SUPUESTO - ajustar con un estudio de muestreo de trabajo</t>
+  </si>
+  <si>
+    <t>Se definen los módulos/plantas/alas del centro. El modelo usa esto para calcular cuánto tarda el personal en llegar a una caída según dónde ocurre y dónde está el personal en ese momento.</t>
+  </si>
+  <si>
+    <t>La columna To-Be debe reflejar el layout rediseñado (unidades de convivencia más pequeñas, sub-almacenes descentralizados, personal más repartido) - normalmente son distancias menores.</t>
+  </si>
+  <si>
+    <t>Distancia a control' = distancia media caminando desde el puesto de control/enfermería hasta el centro de esa zona (medida sobre plano, con podómetro, o de de los planos del edificio).</t>
+  </si>
+  <si>
+    <t>Personal turno DÍA/NOCHE es el nº de auxiliares/enfermeras cuya base está en esa zona durante ese turno cuando no están atendiendo ninguna incidencia. La suma debe coincidir con el personal total de día/noche que definas para la simulación.</t>
+  </si>
+  <si>
+    <t>Puedes añadir o quitar filas de zonas; el script lee todas las filas entre la cabecera y la fila total, así que inserta filas nuevas por encima de la fila total.</t>
+  </si>
+  <si>
+    <t>Distancia intra-zona' = distancia media que recorre el personal dentro de la misma zona donde ya se encuentra (p. ej., de una habitación a otra del mismo módulo), a diferencia de 'Distancia a control', que es hasta el punto de control/enfermería.</t>
+  </si>
+  <si>
+    <t>Dato del centro editable- política interna de frecuencia de rondas.</t>
+  </si>
+  <si>
+    <t>Probabilidad de poder activar dispositivo manual</t>
+  </si>
+  <si>
+    <t>SUPUESTO razonado (no medido): se estima mayor probabilidad de deteccion acustica incidental de noche (silencio ambiental, 1 auxiliar de planta mas cerca) que de dia (ruido de fondo: TV, comidas, conversaciones; personal disperso en tareas simultaneas).</t>
+  </si>
+  <si>
+    <t>Literatura: precision del radar mmWave IWR6843 &gt;95% (Sun et al., 2020) -&gt; se asume el 5% restante como falso negativo.</t>
+  </si>
+  <si>
+    <t>Nº incidencias objetivo
+(solo Escenario de estrés)</t>
+  </si>
+  <si>
+    <t>Escenario de estrés-Brote gastrointestinal o episodio de agitación grupal: varias incidencias concentradas en pocas horas, con el personal de noche ya reducido.</t>
+  </si>
+  <si>
+    <t>Solo aplica si el modo To-Be es 'dispositivo_manual'. Probabilidad de que, en el momento de caer, el residente esté consciente, lleve el dispositivo puesto y pueda pulsarlo. Valor por defecto (0,20) válido para cualquier centro (ver fuente). Si tu centro conoce su propio reparto de residentes por perfil de dependencia (colaborador / no colaborador / con alteración conductual, o una escala equivalente como Barthel o GDS), sustitúyelo por el % de residentes con perfil colaborador de tu propia población: es el perfil que conserva la capacidad cognitiva y física suficiente para activar conscientemente el dispositivo tras una caída. Si tu centro no usa este modo de detección, déjalo en blanco.</t>
+  </si>
+  <si>
+    <t>Supuesto razonado (extrapolación, no medición directa): se toma la prevalencia del perfil de residente «colaborador» (20%) del «Estudio sobre el personal mínimo necesario en las residencias de mayores de la Comunidad de Madrid» (CCOO Madrid, UGT Madrid, PLADIGMARE y SEGG, 2024; n&gt;700 cuestionarios/entrevistas al personal del sector), ya utilizado en este trabajo para el KPI-2. El estudio no mide la capacidad de activar un dispositivo de alarma; la equivalencia colaborador≈capaz de activarlo es una aproximación razonada, declarada como tal, sustituible por el dato propio de cada centro.</t>
+  </si>
+  <si>
+    <t>Escenarios: define las ventanas horarias y condiciones de los 3 escenarios simulados (día tipo, noche tipo, pico de incidencias).</t>
+  </si>
+  <si>
+    <t>4. Las celdas que son supuestos del modelo (no datos medidos), revísalas con más atención, pueden cambiar el resultado si están mal calibradas.</t>
+  </si>
+  <si>
+    <r>
+      <t>Este Excel reúne todos los datos de entrada que necesita el script '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>simulacion_onacare_v5_fix.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="1"/>
+      </rPr>
+      <t>' para simular la respuesta ante caídas de cualquier centro geriátrico. Viene pre-rellenado con los datos (reales y estimados, indicados en cada caso) del centro OnaCare de Barberá del Vallés, a modo de ejemplo funcional.</t>
+    </r>
+  </si>
+  <si>
+    <t>Dentro de las caídas "no presenciadas" (nadie la ve en el momento), una parte se detecta igualmente pronto porque alguien oye un golpe o un grito de ayuda sin haber visto la caída en sí. Esta probabilidad depende del turno: de noche hay más silencio ambiental y el auxiliar de planta está más cerca; de día hay más ruido de fondo (televisión, comidas, conversaciones) y el personal está más disperso en tareas simultáneas. (Supuesto razonado, ver hoja "Deteccion")</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -940,13 +681,6 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF595959"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color rgb="FFBBBEBF"/>
       <name val="Consolas"/>
@@ -978,12 +712,43 @@
     <font>
       <i/>
       <sz val="9"/>
-      <color rgb="FF595959"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -994,18 +759,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
         <bgColor rgb="FF003366"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79989013336588644"/>
-        <bgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFDEADA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1042,7 +795,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1065,44 +818,50 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1377,7 +1136,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
@@ -1389,8 +1148,8 @@
       </c>
     </row>
     <row r="4" spans="1:1" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>163</v>
+      <c r="A4" s="20" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
@@ -1407,23 +1166,23 @@
       </c>
     </row>
     <row r="8" spans="1:1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>3</v>
+      <c r="A8" s="33" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>4</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>150</v>
+      <c r="A10" s="20" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>5</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
@@ -1431,32 +1190,32 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>154</v>
+      <c r="A17" s="20" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -1466,7 +1225,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1479,244 +1238,245 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="10">
+        <v>13</v>
+      </c>
+      <c r="B3" s="28">
         <v>103</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B4" s="7">
         <v>1.5</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B5" s="7">
         <v>70</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>26</v>
+        <v>141</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B6" s="7">
         <v>0.2</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>31</v>
+        <v>25</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B7" s="7">
         <v>5</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>35</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B8" s="7">
         <v>15</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>35</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="B9" s="7">
         <v>0.28999999999999998</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="B10" s="7">
         <v>0.2</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>42</v>
+        <v>35</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B11" s="7">
         <v>365</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B12" s="7">
         <v>300</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" s="8"/>
+        <v>43</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B13" s="7">
         <v>12345</v>
       </c>
       <c r="C13" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="13">
+      <c r="B14" s="28">
         <v>0.2</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>53</v>
+        <v>143</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1732,46 +1492,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
+      <c r="A1" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="62.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
         <v>55</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
-        <v>63</v>
       </c>
       <c r="B3" s="7">
         <v>34</v>
@@ -1798,8 +1558,8 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
-        <v>64</v>
+      <c r="A4" s="12" t="s">
+        <v>56</v>
       </c>
       <c r="B4" s="7">
         <v>34</v>
@@ -1826,8 +1586,8 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>65</v>
+      <c r="A5" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="B5" s="7">
         <v>35</v>
@@ -1854,101 +1614,101 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="16">
+      <c r="A6" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="14">
         <f>SUM(B3:B5)</f>
         <v>103</v>
       </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="16">
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="14">
         <f>SUM(E3:E5)</f>
         <v>12</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="14">
         <f>SUM(F3:F5)</f>
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="15" t="str">
+        <v>59</v>
+      </c>
+      <c r="B7" s="13" t="str">
         <f>IF(B6=Parametros_Generales!B3,"OK","REVISA: no coincide")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
-        <v>68</v>
+      <c r="A9" s="13" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
+      <c r="A10" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
     </row>
     <row r="11" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
+      <c r="A11" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
     </row>
     <row r="12" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
+      <c r="A12" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
     </row>
     <row r="13" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
+      <c r="A13" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
     </row>
     <row r="14" spans="1:8" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
+      <c r="A14" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
     </row>
     <row r="15" spans="1:8" ht="32.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
+      <c r="A15" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1967,8 +1727,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1978,264 +1738,275 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
+      <c r="A1" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
     </row>
     <row r="2" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="E2" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="22">
+        <v>0.75</v>
+      </c>
+      <c r="C4" s="22">
+        <v>0.75</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="22">
+        <v>60</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" s="22">
+        <v>90</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B8" s="22">
+        <v>3</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="E8" s="30" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="25">
+        <v>5</v>
+      </c>
+      <c r="D9" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="26" t="s">
+      <c r="E9" s="30" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="25">
+        <v>30</v>
+      </c>
+      <c r="D10" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="E10" s="30" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="25">
+        <v>0.5</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="147" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="E12" s="30" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" s="24">
+        <v>0.45</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
+      <c r="E13" s="30" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="24">
+        <v>1</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="B4" s="27">
-        <v>0.75</v>
-      </c>
-      <c r="C4" s="27">
-        <v>0.75</v>
-      </c>
-      <c r="D4" s="19" t="s">
+      <c r="E14" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="E4" s="19" t="s">
+    </row>
+    <row r="15" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="B15" s="24">
+        <v>5</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="30" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="B5" s="27">
-        <v>60</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="19" t="s">
+      <c r="E15" s="30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="19" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="B6" s="27">
-        <v>90</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="19" t="s">
+      <c r="B16" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="24">
+        <v>0.05</v>
+      </c>
+      <c r="D16" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="31" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="B7" s="27">
-        <v>0.5</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="B8" s="27">
-        <v>3</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="27">
-        <v>5</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="27">
-        <v>30</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="147" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="B12" s="28">
-        <v>0.15</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26" t="s">
-        <v>139</v>
-      </c>
-      <c r="B13" s="29">
-        <v>0.45</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="26" t="s">
-        <v>137</v>
-      </c>
-      <c r="B14" s="29">
-        <v>1</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="B15" s="29">
-        <v>5</v>
-      </c>
-      <c r="C15" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="29">
-        <v>0.05</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>97</v>
-      </c>
+      <c r="E16" s="30" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+    </row>
+    <row r="18" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2243,7 +2014,6 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2260,93 +2030,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
+      <c r="A1" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
     </row>
     <row r="2" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>103</v>
+        <v>87</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>156</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>108</v>
+      <c r="A3" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>111</v>
+      <c r="A4" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="E5" s="20">
+      <c r="A5" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" s="17">
         <v>8</v>
       </c>
-      <c r="F5" s="18" t="s">
-        <v>111</v>
+      <c r="F5" s="16" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2369,157 +2139,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>161</v>
+      <c r="A1" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15">
+      <c r="A5" s="13">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15">
+      <c r="A6" s="13">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15">
+      <c r="A7" s="13">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15">
+      <c r="A8" s="13">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15">
+      <c r="A9" s="13">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15">
+      <c r="A10" s="13">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="15">
+      <c r="A11" s="13">
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15">
+      <c r="A12" s="13">
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="15">
+      <c r="A13" s="13">
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="15">
+      <c r="A14" s="13">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="15">
+      <c r="A15" s="13">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="15">
+      <c r="A16" s="13">
         <v>15</v>
       </c>
-      <c r="B16" s="23" t="s">
-        <v>128</v>
+      <c r="B16" s="20" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="15">
+      <c r="A17" s="13">
         <v>16</v>
       </c>
-      <c r="B17" s="23" t="s">
-        <v>130</v>
+      <c r="B17" s="20" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="69" x14ac:dyDescent="0.3">
-      <c r="A18" s="15">
+      <c r="A18" s="13">
         <v>17</v>
       </c>
-      <c r="B18" s="23" t="s">
-        <v>131</v>
+      <c r="B18" s="20" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B19" s="22"/>
+      <c r="B19" s="19"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B20" s="22"/>
+      <c r="B20" s="19"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B21" s="22"/>
+      <c r="B21" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
